--- a/Seep-Logos-agents/marketing/sns/templates/anime-launch-templates.xlsx
+++ b/Seep-Logos-agents/marketing/sns/templates/anime-launch-templates.xlsx
@@ -469,11 +469,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
     <col width="32" customWidth="1" min="3" max="3"/>
     <col width="65" customWidth="1" min="4" max="4"/>
   </cols>
@@ -481,7 +481,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>新作アニメ X投稿テンプレート集（汎用版）</t>
+          <t>新作アニメ X投稿テンプレート集（汎用版）全65パターン</t>
         </is>
       </c>
     </row>
@@ -1054,6 +1054,1136 @@
 詳細はこちら▼
 [URL]
 [ハッシュタグ] #キャンペーン</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Phase 7：キャラクター紹介</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>キャラクター紹介（単体）</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>A：シンプルキャラ紹介型</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>TVアニメ『[作品タイトル]』登場キャラクターをご紹介します！
+[キャラクター名]（CV：[声優名]）
+[キャラクターの一言紹介文]
+▼詳細は公式サイトをご確認ください
+[公式サイトURL]
+[ハッシュタグ] #[作品タイトル]キャラクター</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Phase 7：キャラクター紹介</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>キャラクター紹介（単体）</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>B：キャラビジュアル公開型</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>TVアニメ『[作品タイトル]』[キャラクター名]のキャラクタービジュアルを公開しました！
+[キャラクター名]：[声優名]
+▼詳細は公式サイトをご確認ください
+[公式サイトURL]
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Phase 7：キャラクター紹介</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>キャラクター紹介（単体）</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>C：声優コメント紹介型</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>TVアニメ『[作品タイトル]』[キャラクター名]役、[声優名]さんよりコメントが届きました！
+「[コメント内容]」
+[ハッシュタグ] #[作品タイトル]キャスト</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Phase 7：キャラクター紹介</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>キャラクター紹介（複数）</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>A：メインキャラ一覧公開型</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>TVアニメ『[作品タイトル]』登場キャラクター情報を更新しました！
+[キャラクター名]（CV：[声優名]）
+[キャラクター名]（CV：[声優名]）
+[キャラクター名]（CV：[声優名]）
+▼詳細は公式サイトをご確認ください
+[公式サイトURL]
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Phase 8：主題歌・音楽情報</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>OP/ED情報</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>A：OP曲情報公開型</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>TVアニメ『[作品タイトル]』オープニング主題歌情報を公開しました！
+OP：「[曲名]」
+歌：[アーティスト名]
+[ハッシュタグ] #[作品タイトル]OP</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Phase 8：主題歌・音楽情報</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>OP/ED情報</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>B：ED曲情報公開型</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>TVアニメ『[作品タイトル]』エンディング主題歌情報を公開しました！
+ED：「[曲名]」
+歌：[アーティスト名]
+[ハッシュタグ] #[作品タイトル]ED</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Phase 8：主題歌・音楽情報</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>OP/ED情報</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>C：OP/ED同時公開型</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>TVアニメ『[作品タイトル]』主題歌情報を公開しました！
+OP：「[OP曲名]」／[OPアーティスト名]
+ED：「[ED曲名]」／[EDアーティスト名]
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Phase 8：主題歌・音楽情報</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>サウンドトラック・音楽リリース</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>A：サントラ発売告知型</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>TVアニメ『[作品タイトル]』オリジナルサウンドトラックの発売が決定しました！
+■発売日：[発売日]
+■収録曲数：[X]曲
+▼詳細はこちら
+[URL]
+[ハッシュタグ] #[作品タイトル]サントラ</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Phase 8：主題歌・音楽情報</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>サウンドトラック・音楽リリース</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>B：楽曲配信告知型</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>TVアニメ『[作品タイトル]』主題歌「[曲名]」が各種音楽配信サービスにて配信中です！
+▼視聴・ダウンロードはこちら
+[URL]
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Phase 9：グッズ・商品告知</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>グッズ告知</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>A：新グッズ発表型</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>【グッズ情報】
+『[作品タイトル]』[グッズ名]の発売が決定しました！
+■発売日：[発売日]
+■価格：[価格]
+■取扱：[販売店/通販サイト]
+詳細はこちら▼
+[URL]
+[ハッシュタグ] #[作品タイトル]グッズ</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Phase 9：グッズ・商品告知</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>グッズ告知</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>B：予約開始告知型</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>『[作品タイトル]』[グッズ名]の予約受付を開始しました！
+■予約締切：[締切日]
+■発売予定：[発売日]
+▼予約はこちら
+[URL]
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>Phase 9：グッズ・商品告知</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>グッズ告知</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>C：コラボカフェ告知型</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>【コラボカフェ開催決定！】
+『[作品タイトル]』コラボカフェを[場所]にて開催します！
+■期間：[開始日]〜[終了日]
+■場所：[会場名]
+詳細はこちら▼
+[URL]
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>Phase 9：グッズ・商品告知</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>グッズ告知</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>D：コラボカフェ告知型（複数店舗）</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>【コラボカフェ開催！】
+『[作品タイトル]』コラボカフェが全国[X]店舗にて開催中！
+■期間：[開始日]〜[終了日]
+▼参加店舗・詳細はこちら
+[URL]
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Phase 10：舞台挨拶・イベント告知</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>舞台挨拶告知</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>A：舞台挨拶開催告知型</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>【舞台挨拶開催決定！】
+TVアニメ『[作品タイトル]』の舞台挨拶が決定しました！
+■日時：[日付]（[曜日]）[時刻]〜
+■会場：[会場名]
+■登壇：[登壇者名]
+詳細はこちら▼
+[URL]
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>Phase 10：舞台挨拶・イベント告知</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>舞台挨拶告知</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>B：舞台挨拶チケット発売告知型</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>『[作品タイトル]』舞台挨拶のチケット販売が[日付]より開始します！
+▼チケット購入はこちら
+[URL]
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>Phase 10：舞台挨拶・イベント告知</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>舞台挨拶告知</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>C：舞台挨拶終了報告型</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>『[作品タイトル]』舞台挨拶にお越しいただきありがとうございました！
+ご来場いただいた皆さん、ありがとうございます。
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>Phase 10：舞台挨拶・イベント告知</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>イベント・ライブ告知</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>A：イベント開催告知型</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>【イベント開催決定！】
+『[作品タイトル]』[イベント名]の開催が決定しました！
+■日時：[日付]（[曜日]）
+■会場：[会場名]
+詳細は公式サイトをご確認ください▼
+[公式サイトURL]
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>Phase 10：舞台挨拶・イベント告知</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>イベント・ライブ告知</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>B：ライブ・コンサート告知型</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>【ライブイベント開催決定！】
+『[作品タイトル]』[ライブイベント名]の開催が決定しました！
+■日時：[日付]
+■会場：[会場名]
+▼チケット・詳細はこちら
+[URL]
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>Phase 10：舞台挨拶・イベント告知</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>イベント・ライブ告知</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>C：イベント終了報告型</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>『[作品タイトル]』[イベント名]にご来場いただいた皆さん、ありがとうございました！
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Phase 11：再放送・見逃し配信</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>再放送告知</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>A：再放送告知型（スタンダード）</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>TVアニメ『[作品タイトル]』の再放送が決定しました！
+■放送局：[放送局名]
+■放送開始：[日付]（[曜日]）[時刻]〜
+[ハッシュタグ] #[作品タイトル]再放送</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>Phase 11：再放送・見逃し配信</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>再放送告知</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>B：一挙放送告知型</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>『[作品タイトル]』一挙放送が決定しました！
+■放送日：[日付]（[曜日]）
+■放送局：[放送局名]
+■内容：全[X]話一挙放送
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>Phase 11：再放送・見逃し配信</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>配信告知</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>A：見逃し配信告知型</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>TVアニメ『[作品タイトル]』が[配信サービス名]にて見逃し配信中！
+見逃した方はこちらからご覧ください▼
+[配信URL]
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>Phase 11：再放送・見逃し配信</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>配信告知</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>B：全話配信開始告知型</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>TVアニメ『[作品タイトル]』全[X]話が[配信サービス名]にて配信開始しました！
+▼視聴はこちら
+[配信URL]
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Phase 12：コラボ情報</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>コラボ告知</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>A：コラボ発表型（スタンダード）</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>【コラボ情報】
+『[作品タイトル]』×『[コラボ作品名]』コラボレーションの実施が決定しました！
+詳細は公式サイトをご確認ください▼
+[公式サイトURL]
+[ハッシュタグ] #[コラボ作品名]</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>Phase 12：コラボ情報</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>コラボ告知</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>B：コラボグッズ告知型</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>【コラボグッズ情報！】
+『[作品タイトル]』×『[コラボ先]』のコラボグッズが登場！
+■販売開始：[日付]
+■取扱：[販売店]
+詳細はこちら▼
+[URL]
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>Phase 12：コラボ情報</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>コラボ告知</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>C：コラボカフェメニュー公開型</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>『[作品タイトル]』コラボカフェのメニューを公開しました！
+[メニュー名1]、[メニュー名2]など全[X]種類！
+詳細はこちら▼
+[URL]
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Phase 13：周年・記念日</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>放送周年</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>A：放送X周年告知型</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>TVアニメ『[作品タイトル]』放送[X]周年を迎えました！
+いつも応援していただき、ありがとうございます。
+[ハッシュタグ] #[作品タイトル][X]周年</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>Phase 13：周年・記念日</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>放送周年</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>B：周年記念企画告知型</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>【[X]周年記念企画！】
+TVアニメ『[作品タイトル]』放送[X]周年を記念して特別企画を実施します！
+■内容：[概要]
+■期間：[開始日]〜[終了日]
+詳細はこちら▼
+[URL]
+[ハッシュタグ] #[作品タイトル][X]周年</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>Phase 13：周年・記念日</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>キャラクター誕生日</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>A：キャラ誕生日告知型</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>本日は[キャラクター名]の誕生日です！
+お誕生日おめでとうございます！
+[ハッシュタグ] #[キャラクター名]誕生日</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>Phase 13：周年・記念日</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>キャラクター誕生日</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>B：キャラ誕生日ビジュアル公開型</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>本日[X]月[X]日は[キャラクター名]の誕生日！
+お誕生日を記念してイラストを公開しました！
+[ハッシュタグ] #[キャラクター名]誕生日</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>Phase 14：続編・新シーズン発表</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>続編告知</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>A：第2期決定発表型</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>TVアニメ『[作品タイトル]』第2期の制作が決定しました！
+詳細は続報をお待ちください。
+[ハッシュタグ] #[作品タイトル]2期</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>Phase 14：続編・新シーズン発表</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>続編告知</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>B：劇場版決定発表型</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>TVアニメ『[作品タイトル]』の劇場版制作が決定しました！
+詳細は続報をお待ちください！
+[ハッシュタグ] #[作品タイトル]劇場版</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>Phase 14：続編・新シーズン発表</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>続編告知</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>C：続編放送時期告知型</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>TVアニメ『[作品タイトル]』第2期は[放送時期]放送予定です！
+続報は公式アカウントでお知らせします。フォローしてお待ちください！
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>Phase 15：BD/DVD・円盤情報</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>BD/DVD告知</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>A：BD/DVD発売決定型</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>TVアニメ『[作品タイトル]』Blu-ray＆DVDの発売が決定しました！
+■Vol.1発売日：[発売日]
+■価格：[価格]
+▼詳細はこちら
+[URL]
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>Phase 15：BD/DVD・円盤情報</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>BD/DVD告知</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>B：BD/DVD予約開始告知型</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>TVアニメ『[作品タイトル]』Blu-ray BOXの予約受付を開始しました！
+■発売日：[発売日]
+■予約締切：[締切日]
+▼予約はこちら
+[URL]
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>Phase 15：BD/DVD・円盤情報</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>BD/DVD告知</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>C：BD/DVD発売日告知型</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>本日、TVアニメ『[作品タイトル]』Blu-ray Vol.[X]が発売されました！
+▼購入はこちら
+[URL]
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>Phase 15：BD/DVD・円盤情報</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>BD/DVD告知</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>D：特典情報公開型</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>TVアニメ『[作品タイトル]』Blu-ray&amp;DVD 特典情報を公開しました！
+■映像特典：[内容]
+■書き下ろし特典：[内容]
+詳細はこちら▼
+[URL]
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>Phase 16：メディア掲載・受賞</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>メディア掲載</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>A：雑誌掲載報告型</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr">
+        <is>
+          <t>TVアニメ『[作品タイトル]』が[雑誌名][X]月号に掲載されています！
+ぜひご覧ください！
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>Phase 16：メディア掲載・受賞</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>受賞報告</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>A：アニメ賞受賞報告型</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>TVアニメ『[作品タイトル]』が[賞の名称]を受賞しました！
+いつも応援していただいている皆さんのおかげです。ありがとうございます！
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>Phase 17：日常・運用投稿</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>ファン向け日常投稿</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>A：感想募集型</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>TVアニメ『[作品タイトル]』、ご覧いただいていますか？
+感想は[ハッシュタグ]でツイートしてください！
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>Phase 17：日常・運用投稿</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>ファン向け日常投稿</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>B：公式サイト誘導型</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>TVアニメ『[作品タイトル]』の最新情報は公式サイト・公式アカウントをチェック！
+▼公式サイト
+[公式サイトURL]
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>Phase 17：日常・運用投稿</t>
+        </is>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>ファン向け日常投稿</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>C：フォロワー感謝型</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>公式アカウントのフォロワーが[X]万人を突破しました！
+いつも応援ありがとうございます！
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>Phase 17：日常・運用投稿</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>ファン向け日常投稿</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>D：壁紙配布型</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>TVアニメ『[作品タイトル]』公式壁紙を無料配布中！
+▼ダウンロードはこちら
+[URL]
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>Phase 17：日常・運用投稿</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>ファン向け日常投稿</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>E：ファンアート紹介型</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>素敵なファンアートをご紹介します！
+[ハッシュタグ]をつけて投稿いただいた作品です。
+いつも応援ありがとうございます！
+[ハッシュタグ] #[作品タイトル]ファンアート</t>
         </is>
       </c>
     </row>

--- a/Seep-Logos-agents/marketing/sns/templates/anime-launch-templates.xlsx
+++ b/Seep-Logos-agents/marketing/sns/templates/anime-launch-templates.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -34,8 +34,18 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="16">
     <fill>
       <patternFill/>
     </fill>
@@ -57,8 +67,63 @@
         <fgColor rgb="00F9F9F9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6EAF8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D5E8D4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F8E8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCF3CF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF9E7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDEDEC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDFEFE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4ECF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAF2FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3E0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -80,11 +145,55 @@
         <color rgb="00CCCCCC"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -104,6 +213,47 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -469,7 +619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D68"/>
+  <dimension ref="A1:D102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -481,7 +631,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>新作アニメ X投稿テンプレート集（汎用版）全65パターン</t>
+          <t>新作アニメ X投稿テンプレート集（汎用版）全99パターン</t>
         </is>
       </c>
     </row>
@@ -2184,6 +2334,859 @@
 [ハッシュタグ]をつけて投稿いただいた作品です。
 いつも応援ありがとうございます！
 [ハッシュタグ] #[作品タイトル]ファンアート</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>Phase 18：放送リマインド（専用）</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>放送当日朝告知</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>A：シンプル放送当日朝型</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>本日[時刻]より『[作品タイトル]』第[X]話の放送です！
+ぜひご覧ください！
+[ハッシュタグ] #[放送クール]アニメ</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="5" t="inlineStr">
+        <is>
+          <t>Phase 18：放送リマインド（専用）</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>放送当日朝告知</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>B：視聴方法案内付き型</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>本日第[X]話の放送日です！
+■[放送局]：[時刻]〜
+■[配信サービス]：[配信情報]
+ぜひリアルタイムでご覧ください！
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>Phase 18：放送リマインド（専用）</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>放送当日朝告知</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>C：見どころ一言添え型</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>本日[時刻]より第[X]話の放送です！
+[今回の見どころを一言で]
+ぜひご覧ください！
+[ハッシュタグ] #[作品タイトル]第[X]話</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>Phase 18：放送リマインド（専用）</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>放送1時間前リマインド</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>A：スタンダード型</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>『[作品タイトル]』第[X]話は[時刻]より放送開始です！
+感想は[ハッシュタグ]でつぶやいてください！
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>Phase 18：放送リマインド（専用）</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>放送1時間前リマインド</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>B：視聴方法詳細型</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>まもなく放送開始です！
+■放送：[放送局] [時刻]〜
+■配信：[配信サービス] [配信情報]
+ぜひリアルタイムでお楽しみください！
+[ハッシュタグ] #[作品タイトル]第[X]話</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>Phase 18：放送リマインド（専用）</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="inlineStr">
+        <is>
+          <t>放送1時間前リマインド</t>
+        </is>
+      </c>
+      <c r="C74" s="5" t="inlineStr">
+        <is>
+          <t>C：ハッシュタグ推奨型</t>
+        </is>
+      </c>
+      <c r="D74" s="5" t="inlineStr">
+        <is>
+          <t>『[作品タイトル]』第[X]話「[サブタイトル]」まもなく放送です！
+感想は #[ハッシュタグ] でつぶやいてください。
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>Phase 19：キャスト・スタッフ情報（詳細版）</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>キャスト・スタッフコメント</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>A：声優コメント公開型</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>TVアニメ『[作品タイトル]』[キャラクター名]役、[声優名]さんよりコメントが届きました！
+「[コメント内容]」
+▼キャスト情報は公式サイトをご確認ください
+[公式サイトURL]
+[ハッシュタグ] #[作品タイトル]キャスト</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
+        <is>
+          <t>Phase 19：キャスト・スタッフ情報（詳細版）</t>
+        </is>
+      </c>
+      <c r="B76" s="5" t="inlineStr">
+        <is>
+          <t>キャスト・スタッフコメント</t>
+        </is>
+      </c>
+      <c r="C76" s="5" t="inlineStr">
+        <is>
+          <t>B：監督コメント公開型</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>TVアニメ『[作品タイトル]』[監督名]監督よりコメントが届きました！
+「[コメント内容]」
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>Phase 19：キャスト・スタッフ情報（詳細版）</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>キャスト・スタッフコメント</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>C：シリーズ構成コメント型</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="inlineStr">
+        <is>
+          <t>TVアニメ『[作品タイトル]』シリーズ構成・[名前]さんよりコメントが届きました！
+「[コメント内容]」
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>Phase 19：キャスト・スタッフ情報（詳細版）</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>キャスト追加発表</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>A：追加キャスト発表型</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="inlineStr">
+        <is>
+          <t>TVアニメ『[作品タイトル]』追加キャスト情報を公開しました！
+[キャラクター名]：[声優名]
+[キャラクター名]：[声優名]
+詳細は公式サイトをご確認ください▼
+[公式サイトURL]
+[ハッシュタグ] #[作品タイトル]キャスト</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>Phase 19：キャスト・スタッフ情報（詳細版）</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>キャラクタービジュアル追加</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>A：追加キャラビジュアル型</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="inlineStr">
+        <is>
+          <t>TVアニメ『[作品タイトル]』[キャラクター名]のキャラクタービジュアルを公開しました！
+[キャラクター名]（CV：[声優名]）
+▼詳細は公式サイトをご確認ください
+[公式サイトURL]
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>Phase 20：主題歌・音楽情報（詳細版）</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>楽曲配信・発売</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>A：楽曲配信開始型</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="inlineStr">
+        <is>
+          <t>TVアニメ『[作品タイトル]』[OP/ED]主題歌「[曲名]」（[アーティスト名]）が各種音楽配信サービスにて配信中！
+▼視聴・ダウンロードはこちら
+[URL]
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>Phase 20：主題歌・音楽情報（詳細版）</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>楽曲配信・発売</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>B：CDシングル発売告知型</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>TVアニメ『[作品タイトル]』[OP/ED]主題歌「[曲名]」（[アーティスト名]）のCDが[発売日]に発売されます！
+▼予約・詳細はこちら
+[URL]
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>Phase 20：主題歌・音楽情報（詳細版）</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>楽曲配信・発売</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>C：ノンクレジット映像公開型</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="inlineStr">
+        <is>
+          <t>TVアニメ『[作品タイトル]』[OP/ED]ノンクレジット映像を公開しました！
+▼映像はこちら
+[動画URL]
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>Phase 20：主題歌・音楽情報（詳細版）</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>楽曲配信・発売</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t>D：アーティストコメント公開型</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="inlineStr">
+        <is>
+          <t>TVアニメ『[作品タイトル]』[OP/ED]主題歌「[曲名]」、[アーティスト名]さんよりコメントが届きました！
+「[コメント内容]」
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>Phase 20：主題歌・音楽情報（詳細版）</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>サウンドトラック</t>
+        </is>
+      </c>
+      <c r="C84" s="5" t="inlineStr">
+        <is>
+          <t>A：サントラ予約開始型</t>
+        </is>
+      </c>
+      <c r="D84" s="5" t="inlineStr">
+        <is>
+          <t>TVアニメ『[作品タイトル]』オリジナルサウンドトラックの予約受付を開始しました！
+■発売日：[発売日]
+■収録曲数：[X]曲
+▼予約はこちら
+[URL]
+[ハッシュタグ] #[作品タイトル]サントラ</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>Phase 20：主題歌・音楽情報（詳細版）</t>
+        </is>
+      </c>
+      <c r="B85" s="5" t="inlineStr">
+        <is>
+          <t>サウンドトラック</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t>B：サントラ発売日告知型</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="inlineStr">
+        <is>
+          <t>本日、TVアニメ『[作品タイトル]』オリジナルサウンドトラックが発売されました！
+▼購入はこちら
+[URL]
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>Phase 21：各話放送後（詳細版）</t>
+        </is>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>放送直後感謝（詳細版）</t>
+        </is>
+      </c>
+      <c r="C86" s="5" t="inlineStr">
+        <is>
+          <t>A：見どころ言及型</t>
+        </is>
+      </c>
+      <c r="D86" s="5" t="inlineStr">
+        <is>
+          <t>『[作品タイトル]』第[X]話をご覧いただきありがとうございました！
+[今回の見どころ・印象的なシーンを一言]
+次回第[X+1]話もお楽しみに！
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>Phase 21：各話放送後（詳細版）</t>
+        </is>
+      </c>
+      <c r="B87" s="5" t="inlineStr">
+        <is>
+          <t>放送直後感謝（詳細版）</t>
+        </is>
+      </c>
+      <c r="C87" s="5" t="inlineStr">
+        <is>
+          <t>B：見逃し配信誘導型</t>
+        </is>
+      </c>
+      <c r="D87" s="5" t="inlineStr">
+        <is>
+          <t>『[作品タイトル]』第[X]話をご覧いただきありがとうございました。
+見逃した方は[配信サービス名]でご覧いただけます▼
+[配信URL]
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="5" t="inlineStr">
+        <is>
+          <t>Phase 21：各話放送後（詳細版）</t>
+        </is>
+      </c>
+      <c r="B88" s="5" t="inlineStr">
+        <is>
+          <t>放送直後感謝（詳細版）</t>
+        </is>
+      </c>
+      <c r="C88" s="5" t="inlineStr">
+        <is>
+          <t>C：先行カット公開連動型</t>
+        </is>
+      </c>
+      <c r="D88" s="5" t="inlineStr">
+        <is>
+          <t>『[作品タイトル]』第[X]話をご覧いただきありがとうございました！
+次回第[X+1]話の先行場面カットを公開しました！
+来週[曜日][時刻]もお楽しみに！
+[ハッシュタグ] #[作品タイトル]第[X+1]話</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="inlineStr">
+        <is>
+          <t>Phase 21：各話放送後（詳細版）</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>先行場面カット公開</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>A：場面カット公開型（スタンダード）</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="inlineStr">
+        <is>
+          <t>TVアニメ『[作品タイトル]』第[X]話 先行場面カットを公開しました！
+放送は[曜日][時刻]より[放送局]にて！
+[ハッシュタグ] #[作品タイトル]第[X]話</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="inlineStr">
+        <is>
+          <t>Phase 21：各話放送後（詳細版）</t>
+        </is>
+      </c>
+      <c r="B90" s="5" t="inlineStr">
+        <is>
+          <t>先行場面カット公開</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t>B：あらすじ添え型</t>
+        </is>
+      </c>
+      <c r="D90" s="5" t="inlineStr">
+        <is>
+          <t>TVアニメ『[作品タイトル]』第[X]話「[サブタイトル]」の先行場面カットを公開しました！
+[あらすじを1〜2文で]
+[曜日][時刻]よりお楽しみください！
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="inlineStr">
+        <is>
+          <t>Phase 21：各話放送後（詳細版）</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>折り返し・特別投稿</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t>A：中盤折り返し投稿型</t>
+        </is>
+      </c>
+      <c r="D91" s="5" t="inlineStr">
+        <is>
+          <t>TVアニメ『[作品タイトル]』は第[X]話で折り返しとなります！
+ここまでご視聴いただきありがとうございます。
+後半もお楽しみください！
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
+          <t>Phase 21：各話放送後（詳細版）</t>
+        </is>
+      </c>
+      <c r="B92" s="5" t="inlineStr">
+        <is>
+          <t>折り返し・特別投稿</t>
+        </is>
+      </c>
+      <c r="C92" s="5" t="inlineStr">
+        <is>
+          <t>B：最終回1週前告知型</t>
+        </is>
+      </c>
+      <c r="D92" s="5" t="inlineStr">
+        <is>
+          <t>次回はTVアニメ『[作品タイトル]』最終回です！
+[最終回への期待を一言添える]
+ぜひ最後までお見逃しなく！
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>Phase 22：ファン向け日常投稿（詳細版）</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>アンケート投稿</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>A：推しキャラ問いかけ型</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
+        <is>
+          <t>皆さんに質問です！
+『[作品タイトル]』で一番好きなキャラクターは誰ですか？
+コメントで教えてください！
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t>Phase 22：ファン向け日常投稿（詳細版）</t>
+        </is>
+      </c>
+      <c r="B94" s="5" t="inlineStr">
+        <is>
+          <t>アンケート投稿</t>
+        </is>
+      </c>
+      <c r="C94" s="5" t="inlineStr">
+        <is>
+          <t>B：印象的な場面問いかけ型</t>
+        </is>
+      </c>
+      <c r="D94" s="5" t="inlineStr">
+        <is>
+          <t>皆さんが『[作品タイトル]』の中で特に印象に残っているシーンはどこですか？
+#[ハッシュタグ]でコメントをお聞かせください！
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="5" t="inlineStr">
+        <is>
+          <t>Phase 22：ファン向け日常投稿（詳細版）</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>壁紙配布</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="inlineStr">
+        <is>
+          <t>A：壁紙配布型</t>
+        </is>
+      </c>
+      <c r="D95" s="5" t="inlineStr">
+        <is>
+          <t>TVアニメ『[作品タイトル]』公式壁紙を配布中！
+▼ダウンロードはこちら
+[公式サイトURL]
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="5" t="inlineStr">
+        <is>
+          <t>Phase 22：ファン向け日常投稿（詳細版）</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>感謝・フォロワー報告</t>
+        </is>
+      </c>
+      <c r="C96" s="5" t="inlineStr">
+        <is>
+          <t>A：フォロワー達成感謝型</t>
+        </is>
+      </c>
+      <c r="D96" s="5" t="inlineStr">
+        <is>
+          <t>公式アカウントのフォロワーが[X]万人を突破しました！
+いつも応援いただきありがとうございます。
+引き続きよろしくお願いいたします！
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="5" t="inlineStr">
+        <is>
+          <t>Phase 22：ファン向け日常投稿（詳細版）</t>
+        </is>
+      </c>
+      <c r="B97" s="5" t="inlineStr">
+        <is>
+          <t>感謝・フォロワー報告</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="inlineStr">
+        <is>
+          <t>B：週次情報まとめ型</t>
+        </is>
+      </c>
+      <c r="D97" s="5" t="inlineStr">
+        <is>
+          <t>今週のTVアニメ『[作品タイトル]』情報をまとめました！
+・[情報1]
+・[情報2]
+・[情報3]
+詳細は公式サイトをご確認ください▼
+[公式サイトURL]
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="5" t="inlineStr">
+        <is>
+          <t>Phase 22：ファン向け日常投稿（詳細版）</t>
+        </is>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>ファンアート・UGC紹介</t>
+        </is>
+      </c>
+      <c r="C98" s="5" t="inlineStr">
+        <is>
+          <t>A：ファンアート紹介型</t>
+        </is>
+      </c>
+      <c r="D98" s="5" t="inlineStr">
+        <is>
+          <t>素敵なファンアートをご紹介します！
+[ハッシュタグ]をつけて投稿いただいた作品です。
+いつも応援ありがとうございます！
+[ハッシュタグ] #[作品タイトル]ファンアート</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="5" t="inlineStr">
+        <is>
+          <t>Phase 22：ファン向け日常投稿（詳細版）</t>
+        </is>
+      </c>
+      <c r="B99" s="5" t="inlineStr">
+        <is>
+          <t>ファンアート・UGC紹介</t>
+        </is>
+      </c>
+      <c r="C99" s="5" t="inlineStr">
+        <is>
+          <t>B：ファンアート募集型</t>
+        </is>
+      </c>
+      <c r="D99" s="5" t="inlineStr">
+        <is>
+          <t>『[作品タイトル]』のファンアート募集中！
+[ハッシュタグ]をつけてXに投稿してください。
+公式アカウントでご紹介させていただくことがあります！
+[ハッシュタグ] #[作品タイトル]ファンアート</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="inlineStr">
+        <is>
+          <t>Phase 23：再放送・配信（詳細版）</t>
+        </is>
+      </c>
+      <c r="B100" s="4" t="inlineStr">
+        <is>
+          <t>再放送リマインド</t>
+        </is>
+      </c>
+      <c r="C100" s="5" t="inlineStr">
+        <is>
+          <t>A：再放送開始前リマインド型</t>
+        </is>
+      </c>
+      <c r="D100" s="5" t="inlineStr">
+        <is>
+          <t>TVアニメ『[作品タイトル]』の再放送が[日付]（[曜日]）[時刻]より[放送局]にて始まります！
+ぜひご覧ください！
+[ハッシュタグ] #[作品タイトル]再放送</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="5" t="inlineStr">
+        <is>
+          <t>Phase 23：再放送・配信（詳細版）</t>
+        </is>
+      </c>
+      <c r="B101" s="5" t="inlineStr">
+        <is>
+          <t>再放送リマインド</t>
+        </is>
+      </c>
+      <c r="C101" s="5" t="inlineStr">
+        <is>
+          <t>B：見逃し配信追加告知型</t>
+        </is>
+      </c>
+      <c r="D101" s="5" t="inlineStr">
+        <is>
+          <t>TVアニメ『[作品タイトル]』が[配信サービス名]にて[X]月[X]日より配信開始しました！
+見逃していた方はこちらからご覧いただけます▼
+[配信URL]
+[ハッシュタグ]</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="5" t="inlineStr">
+        <is>
+          <t>Phase 23：再放送・配信（詳細版）</t>
+        </is>
+      </c>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
+          <t>一挙放送告知</t>
+        </is>
+      </c>
+      <c r="C102" s="5" t="inlineStr">
+        <is>
+          <t>A：一挙放送告知型</t>
+        </is>
+      </c>
+      <c r="D102" s="5" t="inlineStr">
+        <is>
+          <t>『[作品タイトル]』全[X]話一挙放送が決定しました！
+■放送日：[日付]（[曜日]）
+■放送局：[放送局名]
+■内容：全[X]話
+[ハッシュタグ]</t>
         </is>
       </c>
     </row>
@@ -2201,359 +3204,1693 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:C113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="72" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>よく使われる定型フレーズ一覧（アニメ向け）</t>
-        </is>
-      </c>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>よく使われる定型フレーズ一覧（アニメ向け）（全110フレーズ）</t>
+        </is>
+      </c>
+      <c r="B1" s="20" t="n"/>
+      <c r="C1" s="21" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
         <is>
           <t>カテゴリ</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="C3" s="8" t="inlineStr">
         <is>
           <t>フレーズ</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>制作決定・アニメ化決定系</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>「TVアニメ化決定！」「TVアニメ化が決定しました！」</t>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>「TVアニメ化決定！」</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>制作決定・アニメ化決定系</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>「TVアニメ化が決定しました！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>制作決定・アニメ化決定系</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>「TVアニメ制作決定！」</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>制作決定・アニメ化決定系</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>「[原作タイトル]がTVアニメ化決定！」</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>制作決定・アニメ化決定系</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>「アニメ化の情報を解禁いたします！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>制作決定・アニメ化決定系</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>「[放送時期]放送予定」</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>制作決定・アニメ化決定系</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>「[放送局/配信]にて放送・配信予定」</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>情報公開・解禁系</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>「ティザービジュアルを公開しました」「キービジュアルを公開しました」</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>「ティザービジュアルを公開しました」</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>情報公開・解禁系</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>「ティザーPVを公開しました」「PV第1弾を公開しました」</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>「キービジュアルを公開しました」</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>情報公開・解禁系</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>「キービジュアル第[X]弾を公開しました」</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>情報公開・解禁系</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>「ティザーPVを公開しました」</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>情報公開・解禁系</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>「PV第1弾を公開しました」</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>情報公開・解禁系</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>「PV第[X]弾を公開しました」</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>情報公開・解禁系</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>「ノンクレジットOP映像を公開しました」</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>情報公開・解禁系</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>「先行場面カットを公開しました」</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>情報公開・解禁系</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>「公式サイトをオープンしました▼」</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>情報公開・解禁系</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>「[X]月[X]日より放送開始です！」</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>告知・お知らせ系</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>「TVアニメ『[作品タイトル]』についてお知らせいたします」</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>告知・お知らせ系</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>「[放送時期]放送予定」</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>告知・お知らせ系</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>「[放送局/配信]にて放送・配信予定」</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>情報公開・解禁系</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>「本日、TVアニメ〇〇の情報を解禁いたします！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>キャスト・スタッフ情報系</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>「キャスト情報を公開しました！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>キャスト・スタッフ情報系</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>「キャスト第[X]弾を公開しました！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>キャスト・スタッフ情報系</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>「[キャラクター名]：[声優名]」</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="n">
+        <v>22</v>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>キャスト・スタッフ情報系</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>「[キャラクター名]役を[声優名]さんが担当します！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="n">
+        <v>23</v>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>キャスト・スタッフ情報系</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>「[声優名]さんよりコメントが届きました！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="n">
+        <v>24</v>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>キャスト・スタッフ情報系</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>「スタッフ情報を公開しました！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>キャスト・スタッフ情報系</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>「監督：[名前] / シリーズ構成：[名前] / キャラクターデザイン：[名前]」</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="n">
+        <v>26</v>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>キャスト・スタッフ情報系</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>「アニメーション制作：[制作スタジオ]」</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>キャスト・スタッフ情報系</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>「詳細は公式サイトをご確認ください▼」</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="n">
+        <v>28</v>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
         <is>
           <t>放送開始系</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>「本日より放送開始です！」「本日[時刻]より第1話放送です！」</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>「本日より放送開始です！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="n">
+        <v>29</v>
+      </c>
+      <c r="B32" s="11" t="inlineStr">
         <is>
           <t>放送開始系</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>「本日[時刻]より第1話放送です！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>放送開始系</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
         <is>
           <t>「[放送クール]アニメいよいよスタートです！」</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="11" t="n">
+        <v>31</v>
+      </c>
+      <c r="B34" s="11" t="inlineStr">
         <is>
           <t>放送開始系</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="C34" s="11" t="inlineStr">
         <is>
           <t>「ついに放送開始！」</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="11" t="n">
+        <v>32</v>
+      </c>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>放送開始系</t>
+        </is>
+      </c>
+      <c r="C35" s="11" t="inlineStr">
+        <is>
+          <t>「いよいよ本日放送スタートです！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>放送開始系</t>
+        </is>
+      </c>
+      <c r="C36" s="11" t="inlineStr">
+        <is>
+          <t>「第1話は[時刻]より[放送局]にて放送！ぜひご覧ください！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="11" t="n">
+        <v>34</v>
+      </c>
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t>放送開始系</t>
+        </is>
+      </c>
+      <c r="C37" s="11" t="inlineStr">
+        <is>
+          <t>「[放送局]：[曜日] [時刻]〜 / [配信サービス]：[配信情報]」</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>放送開始系</t>
+        </is>
+      </c>
+      <c r="C38" s="11" t="inlineStr">
+        <is>
+          <t>「放送・配信情報をまとめました！▼公式サイトをご確認ください」</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="B39" s="12" t="inlineStr">
         <is>
           <t>各話放送後の定型フレーズ</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="C39" s="12" t="inlineStr">
+        <is>
+          <t>「第[X]話をご覧いただきありがとうございました！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="12" t="n">
+        <v>37</v>
+      </c>
+      <c r="B40" s="12" t="inlineStr">
+        <is>
+          <t>各話放送後の定型フレーズ</t>
+        </is>
+      </c>
+      <c r="C40" s="12" t="inlineStr">
         <is>
           <t>「第[X]話をご覧いただきありがとうございました」</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="B41" s="12" t="inlineStr">
         <is>
           <t>各話放送後の定型フレーズ</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="C41" s="12" t="inlineStr">
         <is>
           <t>「第[X]話、いかがでしたか？」</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="B42" s="12" t="inlineStr">
         <is>
           <t>各話放送後の定型フレーズ</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>「来週も[曜日][時刻]をお楽しみに！」</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="C42" s="12" t="inlineStr">
+        <is>
+          <t>「来週[曜日]も[時刻]からです。お楽しみに！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="B43" s="12" t="inlineStr">
         <is>
           <t>各話放送後の定型フレーズ</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="C43" s="12" t="inlineStr">
         <is>
           <t>「次回第[X]話もお楽しみに！」</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="12" t="n">
+        <v>41</v>
+      </c>
+      <c r="B44" s="12" t="inlineStr">
+        <is>
+          <t>各話放送後の定型フレーズ</t>
+        </is>
+      </c>
+      <c r="C44" s="12" t="inlineStr">
+        <is>
+          <t>「次回第[X]話「[サブタイトル]」は[日付]（[曜日]）[時刻]より放送です！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="B45" s="12" t="inlineStr">
+        <is>
+          <t>各話放送後の定型フレーズ</t>
+        </is>
+      </c>
+      <c r="C45" s="12" t="inlineStr">
+        <is>
+          <t>「感想は[ハッシュタグ]でつぶやいてください！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="B46" s="12" t="inlineStr">
+        <is>
+          <t>各話放送後の定型フレーズ</t>
+        </is>
+      </c>
+      <c r="C46" s="12" t="inlineStr">
+        <is>
+          <t>「見逃した方はこちらからご覧いただけます▼ [配信URL]」</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="B47" s="12" t="inlineStr">
+        <is>
+          <t>各話放送後の定型フレーズ</t>
+        </is>
+      </c>
+      <c r="C47" s="12" t="inlineStr">
+        <is>
+          <t>「放送1時間前リマインド：本日[時刻]より放送です！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="B48" s="12" t="inlineStr">
+        <is>
+          <t>各話放送後の定型フレーズ</t>
+        </is>
+      </c>
+      <c r="C48" s="12" t="inlineStr">
+        <is>
+          <t>「今週の放送をお楽しみいただけましたか？」</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="13" t="n">
+        <v>46</v>
+      </c>
+      <c r="B49" s="13" t="inlineStr">
         <is>
           <t>最終回・放送終了系</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>「最終回をご覧いただきありがとうございました」</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="C49" s="13" t="inlineStr">
+        <is>
+          <t>「最終回をご覧いただきありがとうございました！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="13" t="n">
+        <v>47</v>
+      </c>
+      <c r="B50" s="13" t="inlineStr">
         <is>
           <t>最終回・放送終了系</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="C50" s="13" t="inlineStr">
         <is>
           <t>「全[X]話ご覧いただきありがとうございました！」</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="13" t="n">
+        <v>48</v>
+      </c>
+      <c r="B51" s="13" t="inlineStr">
         <is>
           <t>最終回・放送終了系</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="C51" s="13" t="inlineStr">
         <is>
           <t>「[作品タイトル]を応援していただき、ありがとうございました」</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="13" t="n">
+        <v>49</v>
+      </c>
+      <c r="B52" s="13" t="inlineStr">
+        <is>
+          <t>最終回・放送終了系</t>
+        </is>
+      </c>
+      <c r="C52" s="13" t="inlineStr">
+        <is>
+          <t>「全[X]話、たくさんのご支援・ご声援をいただき、本当にありがとうございました」</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="13" t="n">
+        <v>50</v>
+      </c>
+      <c r="B53" s="13" t="inlineStr">
+        <is>
+          <t>最終回・放送終了系</t>
+        </is>
+      </c>
+      <c r="C53" s="13" t="inlineStr">
+        <is>
+          <t>「引き続き『[作品タイトル]』をよろしくお願いいたします」</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="13" t="n">
+        <v>51</v>
+      </c>
+      <c r="B54" s="13" t="inlineStr">
+        <is>
+          <t>最終回・放送終了系</t>
+        </is>
+      </c>
+      <c r="C54" s="13" t="inlineStr">
+        <is>
+          <t>「次回最終回、ぜひご覧ください！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="13" t="n">
+        <v>52</v>
+      </c>
+      <c r="B55" s="13" t="inlineStr">
+        <is>
+          <t>最終回・放送終了系</t>
+        </is>
+      </c>
+      <c r="C55" s="13" t="inlineStr">
+        <is>
+          <t>「『[作品タイトル]』の続報については、引き続き公式アカウントでお知らせします」</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="14" t="n">
+        <v>53</v>
+      </c>
+      <c r="B56" s="14" t="inlineStr">
         <is>
           <t>感謝・報告系</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="C56" s="14" t="inlineStr">
         <is>
           <t>「たくさんのご反響をいただきありがとうございます」</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="14" t="n">
+        <v>54</v>
+      </c>
+      <c r="B57" s="14" t="inlineStr">
         <is>
           <t>感謝・報告系</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="C57" s="14" t="inlineStr">
         <is>
           <t>「引き続きよろしくお願いいたします」</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="14" t="n">
+        <v>55</v>
+      </c>
+      <c r="B58" s="14" t="inlineStr">
         <is>
           <t>感謝・報告系</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="C58" s="14" t="inlineStr">
         <is>
           <t>「今後ともよろしくお願いいたします」</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="14" t="n">
+        <v>56</v>
+      </c>
+      <c r="B59" s="14" t="inlineStr">
+        <is>
+          <t>感謝・報告系</t>
+        </is>
+      </c>
+      <c r="C59" s="14" t="inlineStr">
+        <is>
+          <t>「いつも応援ありがとうございます！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="14" t="n">
+        <v>57</v>
+      </c>
+      <c r="B60" s="14" t="inlineStr">
+        <is>
+          <t>感謝・報告系</t>
+        </is>
+      </c>
+      <c r="C60" s="14" t="inlineStr">
+        <is>
+          <t>「フォロワーが[X]万人を突破しました！ありがとうございます！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="14" t="n">
+        <v>58</v>
+      </c>
+      <c r="B61" s="14" t="inlineStr">
+        <is>
+          <t>感謝・報告系</t>
+        </is>
+      </c>
+      <c r="C61" s="14" t="inlineStr">
+        <is>
+          <t>「いつも応援していただいている皆さんのおかげです」</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="15" t="n">
+        <v>59</v>
+      </c>
+      <c r="B62" s="15" t="inlineStr">
         <is>
           <t>続報予告系</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>「続報をお待ちください」「続報は公式アカウントでお知らせします」</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="C62" s="15" t="inlineStr">
+        <is>
+          <t>「続報をお待ちください」</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="15" t="n">
+        <v>60</v>
+      </c>
+      <c r="B63" s="15" t="inlineStr">
         <is>
           <t>続報予告系</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="C63" s="15" t="inlineStr">
+        <is>
+          <t>「続報は公式アカウントでお知らせします」</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="15" t="n">
+        <v>61</v>
+      </c>
+      <c r="B64" s="15" t="inlineStr">
+        <is>
+          <t>続報予告系</t>
+        </is>
+      </c>
+      <c r="C64" s="15" t="inlineStr">
         <is>
           <t>「詳細は公式サイトをご確認ください▼」</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="15" t="n">
+        <v>62</v>
+      </c>
+      <c r="B65" s="15" t="inlineStr">
         <is>
           <t>続報予告系</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="C65" s="15" t="inlineStr">
         <is>
           <t>「フォローして最新情報をチェック！」</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="15" t="n">
+        <v>63</v>
+      </c>
+      <c r="B66" s="15" t="inlineStr">
         <is>
           <t>続報予告系</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="C66" s="15" t="inlineStr">
         <is>
           <t>「次の情報公開をお楽しみに！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="15" t="n">
+        <v>64</v>
+      </c>
+      <c r="B67" s="15" t="inlineStr">
+        <is>
+          <t>続報予告系</t>
+        </is>
+      </c>
+      <c r="C67" s="15" t="inlineStr">
+        <is>
+          <t>「続報は近日公開予定です」</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="15" t="n">
+        <v>65</v>
+      </c>
+      <c r="B68" s="15" t="inlineStr">
+        <is>
+          <t>続報予告系</t>
+        </is>
+      </c>
+      <c r="C68" s="15" t="inlineStr">
+        <is>
+          <t>「最新情報は公式アカウントでご確認ください」</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="16" t="n">
+        <v>66</v>
+      </c>
+      <c r="B69" s="16" t="inlineStr">
+        <is>
+          <t>主題歌・音楽系</t>
+        </is>
+      </c>
+      <c r="C69" s="16" t="inlineStr">
+        <is>
+          <t>「主題歌情報を公開しました！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="16" t="n">
+        <v>67</v>
+      </c>
+      <c r="B70" s="16" t="inlineStr">
+        <is>
+          <t>主題歌・音楽系</t>
+        </is>
+      </c>
+      <c r="C70" s="16" t="inlineStr">
+        <is>
+          <t>「OP：「[曲名]」 歌：[アーティスト名]」</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="16" t="n">
+        <v>68</v>
+      </c>
+      <c r="B71" s="16" t="inlineStr">
+        <is>
+          <t>主題歌・音楽系</t>
+        </is>
+      </c>
+      <c r="C71" s="16" t="inlineStr">
+        <is>
+          <t>「ED：「[曲名]」 歌：[アーティスト名]」</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="16" t="n">
+        <v>69</v>
+      </c>
+      <c r="B72" s="16" t="inlineStr">
+        <is>
+          <t>主題歌・音楽系</t>
+        </is>
+      </c>
+      <c r="C72" s="16" t="inlineStr">
+        <is>
+          <t>「主題歌「[曲名]」が各種音楽配信サービスにて配信中！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="16" t="n">
+        <v>70</v>
+      </c>
+      <c r="B73" s="16" t="inlineStr">
+        <is>
+          <t>主題歌・音楽系</t>
+        </is>
+      </c>
+      <c r="C73" s="16" t="inlineStr">
+        <is>
+          <t>「オリジナルサウンドトラックの発売が決定しました！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="16" t="n">
+        <v>71</v>
+      </c>
+      <c r="B74" s="16" t="inlineStr">
+        <is>
+          <t>主題歌・音楽系</t>
+        </is>
+      </c>
+      <c r="C74" s="16" t="inlineStr">
+        <is>
+          <t>「■発売日：[発売日] ■収録曲数：[X]曲」</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="16" t="n">
+        <v>72</v>
+      </c>
+      <c r="B75" s="16" t="inlineStr">
+        <is>
+          <t>主題歌・音楽系</t>
+        </is>
+      </c>
+      <c r="C75" s="16" t="inlineStr">
+        <is>
+          <t>「▼視聴・ダウンロードはこちら [URL]」</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="17" t="n">
+        <v>73</v>
+      </c>
+      <c r="B76" s="17" t="inlineStr">
+        <is>
+          <t>BD/DVD・映像ソフト系</t>
+        </is>
+      </c>
+      <c r="C76" s="17" t="inlineStr">
+        <is>
+          <t>「Blu-ray＆DVDの発売が決定しました！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="17" t="n">
+        <v>74</v>
+      </c>
+      <c r="B77" s="17" t="inlineStr">
+        <is>
+          <t>BD/DVD・映像ソフト系</t>
+        </is>
+      </c>
+      <c r="C77" s="17" t="inlineStr">
+        <is>
+          <t>「Blu-ray BOXの予約受付を開始しました！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="17" t="n">
+        <v>75</v>
+      </c>
+      <c r="B78" s="17" t="inlineStr">
+        <is>
+          <t>BD/DVD・映像ソフト系</t>
+        </is>
+      </c>
+      <c r="C78" s="17" t="inlineStr">
+        <is>
+          <t>「本日、Blu-ray Vol.[X]が発売されました！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="17" t="n">
+        <v>76</v>
+      </c>
+      <c r="B79" s="17" t="inlineStr">
+        <is>
+          <t>BD/DVD・映像ソフト系</t>
+        </is>
+      </c>
+      <c r="C79" s="17" t="inlineStr">
+        <is>
+          <t>「Blu-ray &amp; DVD [発売時期]発売予定！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="17" t="n">
+        <v>77</v>
+      </c>
+      <c r="B80" s="17" t="inlineStr">
+        <is>
+          <t>BD/DVD・映像ソフト系</t>
+        </is>
+      </c>
+      <c r="C80" s="17" t="inlineStr">
+        <is>
+          <t>「■予約締切：[締切日] ■発売予定：[発売日]」</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="17" t="n">
+        <v>78</v>
+      </c>
+      <c r="B81" s="17" t="inlineStr">
+        <is>
+          <t>BD/DVD・映像ソフト系</t>
+        </is>
+      </c>
+      <c r="C81" s="17" t="inlineStr">
+        <is>
+          <t>「▼予約はこちら [URL]」</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="17" t="n">
+        <v>79</v>
+      </c>
+      <c r="B82" s="17" t="inlineStr">
+        <is>
+          <t>BD/DVD・映像ソフト系</t>
+        </is>
+      </c>
+      <c r="C82" s="17" t="inlineStr">
+        <is>
+          <t>「特典情報を公開しました！▼詳細はこちら」</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="18" t="n">
+        <v>80</v>
+      </c>
+      <c r="B83" s="18" t="inlineStr">
+        <is>
+          <t>舞台挨拶・イベント系</t>
+        </is>
+      </c>
+      <c r="C83" s="18" t="inlineStr">
+        <is>
+          <t>「【舞台挨拶開催決定！】」</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="18" t="n">
+        <v>81</v>
+      </c>
+      <c r="B84" s="18" t="inlineStr">
+        <is>
+          <t>舞台挨拶・イベント系</t>
+        </is>
+      </c>
+      <c r="C84" s="18" t="inlineStr">
+        <is>
+          <t>「【イベント開催決定！】」</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="18" t="n">
+        <v>82</v>
+      </c>
+      <c r="B85" s="18" t="inlineStr">
+        <is>
+          <t>舞台挨拶・イベント系</t>
+        </is>
+      </c>
+      <c r="C85" s="18" t="inlineStr">
+        <is>
+          <t>「■日時：[日付]（[曜日]）[時刻]〜 ■会場：[会場名]」</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="18" t="n">
+        <v>83</v>
+      </c>
+      <c r="B86" s="18" t="inlineStr">
+        <is>
+          <t>舞台挨拶・イベント系</t>
+        </is>
+      </c>
+      <c r="C86" s="18" t="inlineStr">
+        <is>
+          <t>「■登壇：[登壇者名]」</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="18" t="n">
+        <v>84</v>
+      </c>
+      <c r="B87" s="18" t="inlineStr">
+        <is>
+          <t>舞台挨拶・イベント系</t>
+        </is>
+      </c>
+      <c r="C87" s="18" t="inlineStr">
+        <is>
+          <t>「チケット販売が[日付]より開始します！▼チケット購入はこちら」</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="18" t="n">
+        <v>85</v>
+      </c>
+      <c r="B88" s="18" t="inlineStr">
+        <is>
+          <t>舞台挨拶・イベント系</t>
+        </is>
+      </c>
+      <c r="C88" s="18" t="inlineStr">
+        <is>
+          <t>「舞台挨拶にお越しいただきありがとうございました！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="18" t="n">
+        <v>86</v>
+      </c>
+      <c r="B89" s="18" t="inlineStr">
+        <is>
+          <t>舞台挨拶・イベント系</t>
+        </is>
+      </c>
+      <c r="C89" s="18" t="inlineStr">
+        <is>
+          <t>「ご来場いただいた皆さん、ありがとうございます」</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="19" t="n">
+        <v>87</v>
+      </c>
+      <c r="B90" s="19" t="inlineStr">
+        <is>
+          <t>再放送・配信系</t>
+        </is>
+      </c>
+      <c r="C90" s="19" t="inlineStr">
+        <is>
+          <t>「再放送が決定しました！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="19" t="n">
+        <v>88</v>
+      </c>
+      <c r="B91" s="19" t="inlineStr">
+        <is>
+          <t>再放送・配信系</t>
+        </is>
+      </c>
+      <c r="C91" s="19" t="inlineStr">
+        <is>
+          <t>「一挙放送が決定しました！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="19" t="n">
+        <v>89</v>
+      </c>
+      <c r="B92" s="19" t="inlineStr">
+        <is>
+          <t>再放送・配信系</t>
+        </is>
+      </c>
+      <c r="C92" s="19" t="inlineStr">
+        <is>
+          <t>「■放送局：[放送局名] ■放送開始：[日付]（[曜日]）[時刻]〜」</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="19" t="n">
+        <v>90</v>
+      </c>
+      <c r="B93" s="19" t="inlineStr">
+        <is>
+          <t>再放送・配信系</t>
+        </is>
+      </c>
+      <c r="C93" s="19" t="inlineStr">
+        <is>
+          <t>「[配信サービス名]にて見逃し配信中！▼視聴はこちら」</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="19" t="n">
+        <v>91</v>
+      </c>
+      <c r="B94" s="19" t="inlineStr">
+        <is>
+          <t>再放送・配信系</t>
+        </is>
+      </c>
+      <c r="C94" s="19" t="inlineStr">
+        <is>
+          <t>「全[X]話が[配信サービス名]にて配信開始しました！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="9" t="n">
+        <v>92</v>
+      </c>
+      <c r="B95" s="9" t="inlineStr">
+        <is>
+          <t>コラボ系</t>
+        </is>
+      </c>
+      <c r="C95" s="9" t="inlineStr">
+        <is>
+          <t>「【コラボ情報】『[作品タイトル]』×『[コラボ作品名]』コラボレーション決定！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="9" t="n">
+        <v>93</v>
+      </c>
+      <c r="B96" s="9" t="inlineStr">
+        <is>
+          <t>コラボ系</t>
+        </is>
+      </c>
+      <c r="C96" s="9" t="inlineStr">
+        <is>
+          <t>「コラボグッズが登場！▼詳細はこちら」</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="9" t="n">
+        <v>94</v>
+      </c>
+      <c r="B97" s="9" t="inlineStr">
+        <is>
+          <t>コラボ系</t>
+        </is>
+      </c>
+      <c r="C97" s="9" t="inlineStr">
+        <is>
+          <t>「コラボカフェのメニューを公開しました！▼詳細はこちら」</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>周年・キャラ誕生日系</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>「TVアニメ『[作品タイトル]』放送[X]周年を迎えました！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="n">
+        <v>96</v>
+      </c>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>周年・キャラ誕生日系</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>「[X]周年記念企画を実施します！▼詳細はこちら」</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="n">
+        <v>97</v>
+      </c>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>周年・キャラ誕生日系</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t>「本日は[キャラクター名]の誕生日です！お誕生日おめでとうございます！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="n">
+        <v>98</v>
+      </c>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>周年・キャラ誕生日系</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>「[キャラクター名]誕生日を記念してイラストを公開しました！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="10" t="n">
+        <v>99</v>
+      </c>
+      <c r="B102" s="10" t="inlineStr">
+        <is>
+          <t>続編・新シーズン系</t>
+        </is>
+      </c>
+      <c r="C102" s="10" t="inlineStr">
+        <is>
+          <t>「TVアニメ第2期の制作が決定しました！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="10" t="n">
+        <v>100</v>
+      </c>
+      <c r="B103" s="10" t="inlineStr">
+        <is>
+          <t>続編・新シーズン系</t>
+        </is>
+      </c>
+      <c r="C103" s="10" t="inlineStr">
+        <is>
+          <t>「劇場版制作が決定しました！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="10" t="n">
+        <v>101</v>
+      </c>
+      <c r="B104" s="10" t="inlineStr">
+        <is>
+          <t>続編・新シーズン系</t>
+        </is>
+      </c>
+      <c r="C104" s="10" t="inlineStr">
+        <is>
+          <t>「第2期は[放送時期]放送予定です！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="10" t="n">
+        <v>102</v>
+      </c>
+      <c r="B105" s="10" t="inlineStr">
+        <is>
+          <t>続編・新シーズン系</t>
+        </is>
+      </c>
+      <c r="C105" s="10" t="inlineStr">
+        <is>
+          <t>「続報は公式アカウントでお知らせします。フォローしてお待ちください！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="11" t="n">
+        <v>103</v>
+      </c>
+      <c r="B106" s="11" t="inlineStr">
+        <is>
+          <t>受賞・メディア掲載系</t>
+        </is>
+      </c>
+      <c r="C106" s="11" t="inlineStr">
+        <is>
+          <t>「[賞の名称]を受賞しました！応援いただいた皆さん、ありがとうございます！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="11" t="n">
+        <v>104</v>
+      </c>
+      <c r="B107" s="11" t="inlineStr">
+        <is>
+          <t>受賞・メディア掲載系</t>
+        </is>
+      </c>
+      <c r="C107" s="11" t="inlineStr">
+        <is>
+          <t>「[賞の名称]にノミネートされました！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="11" t="n">
+        <v>105</v>
+      </c>
+      <c r="B108" s="11" t="inlineStr">
+        <is>
+          <t>受賞・メディア掲載系</t>
+        </is>
+      </c>
+      <c r="C108" s="11" t="inlineStr">
+        <is>
+          <t>「[雑誌名][X]月号に掲載されています！ぜひご覧ください！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="12" t="n">
+        <v>106</v>
+      </c>
+      <c r="B109" s="12" t="inlineStr">
+        <is>
+          <t>ファン向け日常投稿系</t>
+        </is>
+      </c>
+      <c r="C109" s="12" t="inlineStr">
+        <is>
+          <t>「感想は[ハッシュタグ]でツイートしてください！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="12" t="n">
+        <v>107</v>
+      </c>
+      <c r="B110" s="12" t="inlineStr">
+        <is>
+          <t>ファン向け日常投稿系</t>
+        </is>
+      </c>
+      <c r="C110" s="12" t="inlineStr">
+        <is>
+          <t>「素敵なファンアートをご紹介します！いつも応援ありがとうございます！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="12" t="n">
+        <v>108</v>
+      </c>
+      <c r="B111" s="12" t="inlineStr">
+        <is>
+          <t>ファン向け日常投稿系</t>
+        </is>
+      </c>
+      <c r="C111" s="12" t="inlineStr">
+        <is>
+          <t>「最新情報は公式サイト・公式アカウントをチェック！」</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="12" t="n">
+        <v>109</v>
+      </c>
+      <c r="B112" s="12" t="inlineStr">
+        <is>
+          <t>ファン向け日常投稿系</t>
+        </is>
+      </c>
+      <c r="C112" s="12" t="inlineStr">
+        <is>
+          <t>「公式壁紙を無料配布中！▼ダウンロードはこちら」</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="12" t="n">
+        <v>110</v>
+      </c>
+      <c r="B113" s="12" t="inlineStr">
+        <is>
+          <t>ファン向け日常投稿系</t>
+        </is>
+      </c>
+      <c r="C113" s="12" t="inlineStr">
+        <is>
+          <t>「TVアニメ『[作品タイトル]』、ご覧いただいていますか？」</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
